--- a/pacjenci/ANTONI KASPRZYK.xlsx
+++ b/pacjenci/ANTONI KASPRZYK.xlsx
@@ -483,10 +483,14 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -523,7 +527,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -563,7 +571,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -603,7 +615,11 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -643,7 +659,11 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -683,7 +703,11 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -723,7 +747,11 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -763,7 +791,11 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -803,7 +835,11 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/ANTONI KASPRZYK.xlsx
+++ b/pacjenci/ANTONI KASPRZYK.xlsx
@@ -413,38 +413,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -452,416 +452,302 @@
           <t>SUVmax</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>08.06.2020</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>DLBLC. Ocena stopnia zaawansowania przed rozpoczęciem leczenia.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  61min od podania 18F-FDG. Glikemia: 113mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Łączące się ze sobą spakietowane i pojedyncze węzły chłonne grup: - po stronie lewej obejmujące grupy 1B, 2, 3, 4, 5, nadobojczykowe wielkości wg PET do 36x104x128, SUV max 11,3 [lm fuz 56]  -  po stronie prawej obejmujące grupy 1B, 2, 3, 4, 5, nadobojczykowe wielkości wg PET do 54x125x116, SUV max 12,2 [lm fuz 59]  Aktywność metaboliczna w topografii ujścia prawej trąbki słuchowej na obszarze średnicy wg PET 16mm, SUV max 9,8. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate pogrubienie błony śluzowej prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne: - położony lewobocznie od łuku aorty średnicy wg PET 13mm, SUV max 4,6,  - w śródpiersiu przednim zamostkowo po stronie lewej średnicy wg PET 21mm, SUV max 6,8, - okna aortalno-płucnego wielkości do 12mm, SUV max do  9,5 - podostrogowe średnicy wg PET 15mm, SUV max 7,4, - przytchawiczy dolny prawy średnicy wg PET 7mm, SUV max 3,0, - pomiędzy aortą a trzonem kręgu Th7 średnicy wg PET 15mm, SUV max 5,0, - wnęki płuca lewego średnicy wg PET 7mm, SUV max 2,7, - wnęki płuca prawego średnicy wg PET 14mm, SUV max 4,3 - pachowe i międzypiersiowe lewe wielkości wg PET do 30x67mm, SUV max 9,6, - pachowe i międzypiersiowe prawe wielkości wg PET do 26x41mm, SUV max 20,9, Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm.  Brzuch i miednica: Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne: - pod prawą kopułą przepony średnicy wg PET do 20mm, SUV max do 7,9, - przy krzywiźnie mniejszej żołądka średnicy wg PET 19mm, SUV max 4,7, - okolicy głowy trzustki średnicy wg PET do 10mm, SUV max 5,8, - przyaortalne, biodrowe wspólne, wewnętrzne i zewnętrzne prawe wielkości wg PET do 55x70mm, SUV max do 25,7 [lm fuz 234], - przyaortalne, biodrowe wspólne, wewnętrzne i zewnętrzne lewe wielkości wg PET do 47x42mm, SUV max do 12,2 [lm fuz 180], - pachwinowe i udowe lewe średnicy wg PET do 14mm, SUV max do 5,4, - pachwinowe prawe średnicy wg PET do 40mm, SUV max do 12,9.  Aktywny metabolicznie guz nadnercza lewego średnicy wg PET 19mm, SUV max 6,4 oraz nadnercza prawego średnicy wg PET 12mm, SUV max 4,0. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym; wyspa kostna w  Th3.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 2,1, Prawy płat wątroby SUVmax do 2,4.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po obu stronach przepony, nadnerczy obustronnie oraz ujścia prawej trąbki słuchowej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>25.7</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>19.10.2020</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>DLBLC. Ocena wczesnej  odpowiedzi po 4 cyklach chemioterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  61min od podania 18F-FDG. Glikemia: 79mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Symetrycznie wzmożona aktywność metaboliczna w strukturach pierścienia Waldeyera SUV max do 5,2. Aktywne metabolicznie węzły chłonne: - 2A po stronie prawej średnicy wg PET do 12mm, SUV max do 4,5; - 2B po stronie lewej średnicy wg PET 10mm, SUV max 3,1. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej. Liczne drobne węzły chłonne szyjne obustronnie średnicy do 10mm. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne: - okna aortalno-płucnego średnicy do 6x10mm, SUV max do  2,4; - przytchawicze dolne prawe średnicy do 9mm, SUV max 2,7; - wnęka płuca lewego, SUV max 2,8, - wnęka płuca prawego SUV max 2,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne: - pomiędzy aortą a trzonem kręgu Th7 średnicy 7mm; - pachowe i międzypiersiowe lewe wielkości do 25x16mm (SUV max 1,9); - pachowe i międzypiersiowe prawe wielkości do 17x10mm (SUV max 1,4). Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Drobny aktywny metabolicznie obszar w topografii opuszki XII-icy/części odźwiernikowej  żołądka, SUV max 4,1 - do oceny endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Guz nadnercza lewego wielkości 25x19mm. Drobne węzły chłonne okołoaortalne i biodrowe wspólne obustronnie średnicy do 13mm. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Wzmożona aktywność metaboliczna w topografii blaszki granicznej górnej  trzonu kręgu L2, SUV max 4,8 - gojące się włamanie blaszki? Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Rozlanie wzmożony metabolizm FDG w obrębie mięśni KLP obustronnie, a zwłaszcza w obrębie mięśnia zębatego przedniego lewego, SUV max do 4,3 - w pierwszej kolejności zmiany przeciążeniowe. Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 2,8.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych i pobudzonych metabolicznie węzłów chłonnych szyi obustronnie oraz klatki piersiowej. W porównaniu do badania wyjściowego  PET/CT z  08.06.2020 - częściowa regresja metaboliczna i radiologiczna opisywanych zmian.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5.2</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>03.02.2021</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>DLBLC. Stan po 8 R-CHOP. Ocena po zakończeniu leczenia.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 114mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywny i miernie pobudzone metabolicznie węzły chłonne: - 2A po stronie prawej wielkości do 11mm, SUV max do 4,8; - 2B po stronie lewej wielkości do 8mm, SUV max do 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej. Pojedyncze drobne węzły chłonne szyjne obustronnie poniżej 10mm. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata.  Klatka piersiowa i śródpiersie: Pobudzony metabolicznie węzeł chłonny przytchawiczy dolny prawy wielkości 7mm, SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne: - pachowe lewe wielkości do 13mm  - pachowe prawe wielkości do 16mm oraz drobne przy łuku aorty i przytchawicze prawe.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły okołoaortalne obustronnie wielkości do 14x21mm po stronie prawej i 14mm po stronie lewej.  Guz nadnercza lewego wielkości 19mm. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Załamanie blaszki granicznej górnej i obniżenie wysokości trzonu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 2,5; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego (szyjny) i miernie pobudzonych metabolicznie węzłów chłonnych szyi oraz pojedynczego klatki piersiowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>4.8</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>08.07.2021</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>DLBLC. Czy jest progresja?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 92mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Pobudzone metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 8mm, SUV max do 3,1. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła - do oceny klinicznej ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Guz nadnercza lewego wielkości 19mm. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Załamanie blaszki granicznej górnej i obniżenie wysokości trzonu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,7 Prawy płat wątroby SUVmax do 2,1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie węzłów chłonnych na szyi. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>3.1</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>11.10.2021</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>DLBLC. Ocena po 8 cyklach R-CHOP.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 119mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 11mm wg PET, SUV max do 5,0. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła, SUV max do 9,5 - do oceny klinicznej i ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej [zatoka prawie całkowicie bezpowietrzna] oraz drobne w lewej. Wydatne przyścienne zgrubienia błony śluzowej w lewej zatoce klinowej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata-do kontroli w USG.  Klatka piersiowa i śródpiersie: Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - wskazana konsultacja kardiologiczna i Echokardiografia. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 3 i 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzony metabolicznie guz nadnercza lewego, wielkości 19x17mm, SUV max 3,5 - do oceny w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 4,0.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie węzłów chłonnych szyjnych. Wskazana konsultacja kardiologiczna - vide opis powyżej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>9.5</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>17.05.2022</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>DLBLC. Ocena po 8 cyklach R-CHOP.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 119mg%.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 11mm wg PET, SUV max do 5,0. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła, SUV max do 9,5 - do oceny klinicznej i ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej [zatoka prawie całkowicie bezpowietrzna] oraz drobne w lewej. Wydatne przyścienne zgrubienia błony śluzowej w lewej zatoce klinowej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata-do kontroli w USG.  Klatka piersiowa i śródpiersie: Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - wskazana konsultacja kardiologiczna i Echokardiografia. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 3 i 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzony metabolicznie guz nadnercza lewego, wielkości 19x17mm, SUV max 3,5 - do oceny w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 4,0.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie węzłów chłonnych szyjnych. Wskazana konsultacja kardiologiczna - vide opis powyżej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>9.5</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>19.09.2022</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>DLBLC. Ocena po 8 cyklach R-CHOP.</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 119mg%.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 11mm wg PET, SUV max do 5,0. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła, SUV max do 9,5 - do oceny klinicznej i ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej [zatoka prawie całkowicie bezpowietrzna] oraz drobne w lewej. Wydatne przyścienne zgrubienia błony śluzowej w lewej zatoce klinowej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata-do kontroli w USG.  Klatka piersiowa i śródpiersie: Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - wskazana konsultacja kardiologiczna i Echokardiografia. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 3 i 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzony metabolicznie guz nadnercza lewego, wielkości 19x17mm, SUV max 3,5 - do oceny w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 4,0.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie węzłów chłonnych szyjnych. Wskazana konsultacja kardiologiczna - vide opis powyżej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>9.5</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>24.04.2023</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>DLBLC. Leczenie zakończone 12.2020. Badanie kontrolne ( gł. ww chłonne szyjne - w badaniu fizykalnym i USG stabilne w PET niejednoznaczne)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 93 mg%.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metabolicznie węzły chłonne grupy 2A po stronie prawej wielkości do 13 mm  SUV max do 7,3 oraz grupy 2 B po stronie lewej wielkości 8x13 mm SUV max 4,6. Wzmożony metabolizm FDG w strukturach pierścienia Waldeyera SUV max do 8,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej, w lewej zatoce klinowej wydzielina śluzowa. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata - do kontroli w USG. Ok. 11mm brodawka skórna przynosowo po stronie lewej twarzy. Węzły chłonne na szyi obustronnie średnicy do 12mm.  Klatka piersiowa i śródpiersie: Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - opisywane już poprzednio. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 16mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Pęcherze rozedmowe w obu płucach, ocena utrudniona przez artefakty oddechowe. AGR Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatniejsze zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku SUV max 3,8. Guz nadnercza lewego, wielkości 26x18mm SUV max 2,5. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo. Wydatne pęcherzyki nasienne. Obustronnie węzły chłonne pachwinowe wielkości do 11mm.  Układ kostny: Wzmożony metabolizm FDG pomiędzy wyrostkami kolczystymi na poziomie L3/L4 SUV max 4,2- zmiany odczynowo-przeciążeniowe? Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Aktywnie metabolicznie obszar w topografii rozwastwionej, uwapnionej blaszki  miażdżycowej w tylnej ścianie aorty na poziomie Th12 wielkości 7x7mm wg. PET, SUV max 5,7 [Im fuz 154] Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnych metabolicznie drobnych węzłów chłonnych na szyi obustronnie - do weryfikacji histopatologicznej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>11.02.2025</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>9</v>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Stan po leczeniu. Aktualnie nawrót objawów: poty nocne, osłabienie, badalne węzły chłonne szyjne.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 108 mg%.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne i pobudzone metabolicznie węzły chłonne szyjne: - węzły własne ślinianek przyusznych- po stronie prawej średnicy 15mm wg PET SUV max 4,1; po stronie lewej średnicy 9mm SUV max 2,9; - grupy 2A po stronie prawej wielkości10x8 mm  SUV max 9,8; - grupy 2A po stronie lewej wielkości 11x12 mm SUV max 6,0. Pobudzona metabolicznie brodawka skórna przynosowo po stronie lewej twarzy wielkości ok 10 mm SUV max 3,1. Wzmożony metabolizm FDG w strukturach pierścienia Waldeyera SUV max do 7,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Polipowate zgrubienie błony śluzowej w lewej zatoce klinowej.  Drobne, polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Ogniskowo zwiększony metabolizm FDG zabrodawkowo w piersi lewej, na obszarze wielkości wg. PET 11mm, SUV max 3,5 - do kontroli w USG/Mammografii. Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - opisywane już poprzednio. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Nieliczne pęcherze rozedmowe w obu płucach. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatniejsze zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w jelitach położonych w miednicy, SUV max 6,9 Guz nadnercza lewego, wielkości 27x18mm, SUV max 2,7. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo. Wydatne pęcherzyki nasienne. Uchyłki esicy. Obustronnie węzły chłonne pachwinowe wielkości do 11x9mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2 do 15mm. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,8.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnych metabolicznie węzłów chłonnych szyi i twarzoczaszki. Ogniskowo zwiększony metabolizm FDG zabrodawkowo w piersi lewej- do kontroli w USG/Mammografii. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/ANTONI KASPRZYK.xlsx
+++ b/pacjenci/ANTONI KASPRZYK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  61min od podania 18F-FDG. Glikemia: 113mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Łączące się ze sobą spakietowane i pojedyncze węzły chłonne grup: - po stronie lewej obejmujące grupy 1B, 2, 3, 4, 5, nadobojczykowe wielkości wg PET do 36x104x128, SUV max 11,3 [lm fuz 56]  -  po stronie prawej obejmujące grupy 1B, 2, 3, 4, 5, nadobojczykowe wielkości wg PET do 54x125x116, SUV max 12,2 [lm fuz 59]  Aktywność metaboliczna w topografii ujścia prawej trąbki słuchowej na obszarze średnicy wg PET 16mm, SUV max 9,8. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate pogrubienie błony śluzowej prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne: - położony lewobocznie od łuku aorty średnicy wg PET 13mm, SUV max 4,6,  - w śródpiersiu przednim zamostkowo po stronie lewej średnicy wg PET 21mm, SUV max 6,8, - okna aortalno-płucnego wielkości do 12mm, SUV max do  9,5 - podostrogowe średnicy wg PET 15mm, SUV max 7,4, - przytchawiczy dolny prawy średnicy wg PET 7mm, SUV max 3,0, - pomiędzy aortą a trzonem kręgu Th7 średnicy wg PET 15mm, SUV max 5,0, - wnęki płuca lewego średnicy wg PET 7mm, SUV max 2,7, - wnęki płuca prawego średnicy wg PET 14mm, SUV max 4,3 - pachowe i międzypiersiowe lewe wielkości wg PET do 30x67mm, SUV max 9,6, - pachowe i międzypiersiowe prawe wielkości wg PET do 26x41mm, SUV max 20,9, Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm.  Brzuch i miednica: Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne: - pod prawą kopułą przepony średnicy wg PET do 20mm, SUV max do 7,9, - przy krzywiźnie mniejszej żołądka średnicy wg PET 19mm, SUV max 4,7, - okolicy głowy trzustki średnicy wg PET do 10mm, SUV max 5,8, - przyaortalne, biodrowe wspólne, wewnętrzne i zewnętrzne prawe wielkości wg PET do 55x70mm, SUV max do 25,7 [lm fuz 234], - przyaortalne, biodrowe wspólne, wewnętrzne i zewnętrzne lewe wielkości wg PET do 47x42mm, SUV max do 12,2 [lm fuz 180], - pachwinowe i udowe lewe średnicy wg PET do 14mm, SUV max do 5,4, - pachwinowe prawe średnicy wg PET do 40mm, SUV max do 12,9.  Aktywny metabolicznie guz nadnercza lewego średnicy wg PET 19mm, SUV max 6,4 oraz nadnercza prawego średnicy wg PET 12mm, SUV max 4,0. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym; wyspa kostna w  Th3.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 2,1, Prawy płat wątroby SUVmax do 2,4.</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Łączące się ze sobą spakietowane i pojedyncze węzły chłonne grup: - po stronie lewej obejmujące grupy 1B, 2, 3, 4, 5, nadobojczykowe wielkości wg PET do 36x104x128, SUV max 11,3 [lm fuz 56]  -  po stronie prawej obejmujące grupy 1B, 2, 3, 4, 5, nadobojczykowe wielkości wg PET do 54x125x116, SUV max 12,2 [lm fuz 59]  Aktywność metaboliczna w topografii ujścia prawej trąbki słuchowej na obszarze średnicy wg PET 16mm, SUV max 9,8. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate pogrubienie błony śluzowej prawej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne: - położony lewobocznie od łuku aorty średnicy wg PET 13mm, SUV max 4,6,  - w śródpiersiu przednim zamostkowo po stronie lewej średnicy wg PET 21mm, SUV max 6,8, - okna aortalno-płucnego wielkości do 12mm, SUV max do  9,5 - podostrogowe średnicy wg PET 15mm, SUV max 7,4, - przytchawiczy dolny prawy średnicy wg PET 7mm, SUV max 3,0, - pomiędzy aortą a trzonem kręgu Th7 średnicy wg PET 15mm, SUV max 5,0, - wnęki płuca lewego średnicy wg PET 7mm, SUV max 2,7, - wnęki płuca prawego średnicy wg PET 14mm, SUV max 4,3 - pachowe i międzypiersiowe lewe wielkości wg PET do 30x67mm, SUV max 9,6, - pachowe i międzypiersiowe prawe wielkości wg PET do 26x41mm, SUV max 20,9, Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie spakietowane i pojedyncze węzły chłonne: - pod prawą kopułą przepony średnicy wg PET do 20mm, SUV max do 7,9, - przy krzywiźnie mniejszej żołądka średnicy wg PET 19mm, SUV max 4,7, - okolicy głowy trzustki średnicy wg PET do 10mm, SUV max 5,8, - przyaortalne, biodrowe wspólne, wewnętrzne i zewnętrzne prawe wielkości wg PET do 55x70mm, SUV max do 25,7 [lm fuz 234], - przyaortalne, biodrowe wspólne, wewnętrzne i zewnętrzne lewe wielkości wg PET do 47x42mm, SUV max do 12,2 [lm fuz 180], - pachwinowe i udowe lewe średnicy wg PET do 14mm, SUV max do 5,4, - pachwinowe prawe średnicy wg PET do 40mm, SUV max do 12,9.  Aktywny metabolicznie guz nadnercza lewego średnicy wg PET 19mm, SUV max 6,4 oraz nadnercza prawego średnicy wg PET 12mm, SUV max 4,0. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym; wyspa kostna w  Th3.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po obu stronach przepony, nadnerczy obustronnie oraz ujścia prawej trąbki słuchowej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>25.7</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  61min od podania 18F-FDG. Glikemia: 79mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Symetrycznie wzmożona aktywność metaboliczna w strukturach pierścienia Waldeyera SUV max do 5,2. Aktywne metabolicznie węzły chłonne: - 2A po stronie prawej średnicy wg PET do 12mm, SUV max do 4,5; - 2B po stronie lewej średnicy wg PET 10mm, SUV max 3,1. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej. Liczne drobne węzły chłonne szyjne obustronnie średnicy do 10mm. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Pobudzone metabolicznie węzły chłonne: - okna aortalno-płucnego średnicy do 6x10mm, SUV max do  2,4; - przytchawicze dolne prawe średnicy do 9mm, SUV max 2,7; - wnęka płuca lewego, SUV max 2,8, - wnęka płuca prawego SUV max 2,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne: - pomiędzy aortą a trzonem kręgu Th7 średnicy 7mm; - pachowe i międzypiersiowe lewe wielkości do 25x16mm (SUV max 1,9); - pachowe i międzypiersiowe prawe wielkości do 17x10mm (SUV max 1,4). Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Drobny aktywny metabolicznie obszar w topografii opuszki XII-icy/części odźwiernikowej  żołądka, SUV max 4,1 - do oceny endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Guz nadnercza lewego wielkości 25x19mm. Drobne węzły chłonne okołoaortalne i biodrowe wspólne obustronnie średnicy do 13mm. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Wzmożona aktywność metaboliczna w topografii blaszki granicznej górnej  trzonu kręgu L2, SUV max 4,8 - gojące się włamanie blaszki? Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Rozlanie wzmożony metabolizm FDG w obrębie mięśni KLP obustronnie, a zwłaszcza w obrębie mięśnia zębatego przedniego lewego, SUV max do 4,3 - w pierwszej kolejności zmiany przeciążeniowe. Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 2,0; Prawy płat wątroby SUVmax do 2,8.</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Symetrycznie wzmożona aktywność metaboliczna w strukturach pierścienia Waldeyera SUV max do 5,2. Aktywne metabolicznie węzły chłonne: - 2A po stronie prawej średnicy wg PET do 12mm, SUV max do 4,5; - 2B po stronie lewej średnicy wg PET 10mm, SUV max 3,1. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej. Liczne drobne węzły chłonne szyjne obustronnie średnicy do 10mm. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne: - okna aortalno-płucnego średnicy do 6x10mm, SUV max do  2,4; - przytchawicze dolne prawe średnicy do 9mm, SUV max 2,7; - wnęka płuca lewego, SUV max 2,8, - wnęka płuca prawego SUV max 2,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne: - pomiędzy aortą a trzonem kręgu Th7 średnicy 7mm; - pachowe i międzypiersiowe lewe wielkości do 25x16mm (SUV max 1,9); - pachowe i międzypiersiowe prawe wielkości do 17x10mm (SUV max 1,4). Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Drobny aktywny metabolicznie obszar w topografii opuszki XII-icy/części odźwiernikowej  żołądka, SUV max 4,1 - do oceny endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Guz nadnercza lewego wielkości 25x19mm. Drobne węzły chłonne okołoaortalne i biodrowe wspólne obustronnie średnicy do 13mm. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Wzmożona aktywność metaboliczna w topografii blaszki granicznej górnej  trzonu kręgu L2, SUV max 4,8 - gojące się włamanie blaszki? Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Rozlanie wzmożony metabolizm FDG w obrębie mięśni KLP obustronnie, a zwłaszcza w obrębie mięśnia zębatego przedniego lewego, SUV max do 4,3 - w pierwszej kolejności zmiany przeciążeniowe. Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych i pobudzonych metabolicznie węzłów chłonnych szyi obustronnie oraz klatki piersiowej. W porównaniu do badania wyjściowego  PET/CT z  08.06.2020 - częściowa regresja metaboliczna i radiologiczna opisywanych zmian.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>5.2</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 114mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Aktywny i miernie pobudzone metabolicznie węzły chłonne: - 2A po stronie prawej wielkości do 11mm, SUV max do 4,8; - 2B po stronie lewej wielkości do 8mm, SUV max do 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej. Pojedyncze drobne węzły chłonne szyjne obustronnie poniżej 10mm. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata.  Klatka piersiowa i śródpiersie: Pobudzony metabolicznie węzeł chłonny przytchawiczy dolny prawy wielkości 7mm, SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne: - pachowe lewe wielkości do 13mm  - pachowe prawe wielkości do 16mm oraz drobne przy łuku aorty i przytchawicze prawe.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły okołoaortalne obustronnie wielkości do 14x21mm po stronie prawej i 14mm po stronie lewej.  Guz nadnercza lewego wielkości 19mm. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Załamanie blaszki granicznej górnej i obniżenie wysokości trzonu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 2,5; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Aktywny i miernie pobudzone metabolicznie węzły chłonne: - 2A po stronie prawej wielkości do 11mm, SUV max do 4,8; - 2B po stronie lewej wielkości do 8mm, SUV max do 2,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej. Pojedyncze drobne węzły chłonne szyjne obustronnie poniżej 10mm. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pobudzony metabolicznie węzeł chłonny przytchawiczy dolny prawy wielkości 7mm, SUV max 3,3. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne: - pachowe lewe wielkości do 13mm  - pachowe prawe wielkości do 16mm oraz drobne przy łuku aorty i przytchawicze prawe.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły okołoaortalne obustronnie wielkości do 14x21mm po stronie prawej i 14mm po stronie lewej.  Guz nadnercza lewego wielkości 19mm. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Załamanie blaszki granicznej górnej i obniżenie wysokości trzonu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego (szyjny) i miernie pobudzonych metabolicznie węzłów chłonnych szyi oraz pojedynczego klatki piersiowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>4.8</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 92mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Pobudzone metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 8mm, SUV max do 3,1. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła - do oceny klinicznej ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Guz nadnercza lewego wielkości 19mm. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Załamanie blaszki granicznej górnej i obniżenie wysokości trzonu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,7 Prawy płat wątroby SUVmax do 2,1</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pobudzone metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 8mm, SUV max do 3,1. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła - do oceny klinicznej ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Guz nadnercza lewego wielkości 19mm. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Załamanie blaszki granicznej górnej i obniżenie wysokości trzonu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie węzłów chłonnych na szyi. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>3.1</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 119mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 11mm wg PET, SUV max do 5,0. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła, SUV max do 9,5 - do oceny klinicznej i ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej [zatoka prawie całkowicie bezpowietrzna] oraz drobne w lewej. Wydatne przyścienne zgrubienia błony śluzowej w lewej zatoce klinowej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata-do kontroli w USG.  Klatka piersiowa i śródpiersie: Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - wskazana konsultacja kardiologiczna i Echokardiografia. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 3 i 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzony metabolicznie guz nadnercza lewego, wielkości 19x17mm, SUV max 3,5 - do oceny w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 4,0.</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 11mm wg PET, SUV max do 5,0. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła, SUV max do 9,5 - do oceny klinicznej i ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej [zatoka prawie całkowicie bezpowietrzna] oraz drobne w lewej. Wydatne przyścienne zgrubienia błony śluzowej w lewej zatoce klinowej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata-do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - wskazana konsultacja kardiologiczna i Echokardiografia. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 3 i 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pobudzony metabolicznie guz nadnercza lewego, wielkości 19x17mm, SUV max 3,5 - do oceny w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie węzłów chłonnych szyjnych. Wskazana konsultacja kardiologiczna - vide opis powyżej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -634,20 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 119mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 11mm wg PET, SUV max do 5,0. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła, SUV max do 9,5 - do oceny klinicznej i ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej [zatoka prawie całkowicie bezpowietrzna] oraz drobne w lewej. Wydatne przyścienne zgrubienia błony śluzowej w lewej zatoce klinowej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata-do kontroli w USG.  Klatka piersiowa i śródpiersie: Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - wskazana konsultacja kardiologiczna i Echokardiografia. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 3 i 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzony metabolicznie guz nadnercza lewego, wielkości 19x17mm, SUV max 3,5 - do oceny w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 4,0.</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 11mm wg PET, SUV max do 5,0. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła, SUV max do 9,5 - do oceny klinicznej i ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej [zatoka prawie całkowicie bezpowietrzna] oraz drobne w lewej. Wydatne przyścienne zgrubienia błony śluzowej w lewej zatoce klinowej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata-do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - wskazana konsultacja kardiologiczna i Echokardiografia. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 3 i 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pobudzony metabolicznie guz nadnercza lewego, wielkości 19x17mm, SUV max 3,5 - do oceny w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie węzłów chłonnych szyjnych. Wskazana konsultacja kardiologiczna - vide opis powyżej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -667,20 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 119mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 11mm wg PET, SUV max do 5,0. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła, SUV max do 9,5 - do oceny klinicznej i ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej [zatoka prawie całkowicie bezpowietrzna] oraz drobne w lewej. Wydatne przyścienne zgrubienia błony śluzowej w lewej zatoce klinowej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata-do kontroli w USG.  Klatka piersiowa i śródpiersie: Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - wskazana konsultacja kardiologiczna i Echokardiografia. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 3 i 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzony metabolicznie guz nadnercza lewego, wielkości 19x17mm, SUV max 3,5 - do oceny w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.  Układ kostny: Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 4,0.</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne przedziału 2A po stronie prawej wielkości do 11mm wg PET, SUV max do 5,0. Niejednoznaczny obszar pobudzenia metabolicznego na tylnej ścianie gardła, SUV max do 9,5 - do oceny klinicznej i ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej [zatoka prawie całkowicie bezpowietrzna] oraz drobne w lewej. Wydatne przyścienne zgrubienia błony śluzowej w lewej zatoce klinowej. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata-do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - wskazana konsultacja kardiologiczna i Echokardiografia. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W segm. 4 płuca lewego zwapnienie 5mm. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 10mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Ok. 13mm pęcherz rozedmowy w segm. 3 i 6 płuca prawego. Drobne pęcherze rozedmowe w segm. grzbietowych obu płuc. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatne zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pobudzony metabolicznie guz nadnercza lewego, wielkości 19x17mm, SUV max 3,5 - do oceny w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Nieco niejednorodny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność pobudzonych metabolicznie węzłów chłonnych szyjnych. Wskazana konsultacja kardiologiczna - vide opis powyżej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="L8" t="n">
         <v>9.5</v>
       </c>
     </row>
@@ -700,20 +900,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 93 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>: Aktywne metabolicznie węzły chłonne grupy 2A po stronie prawej wielkości do 13 mm  SUV max do 7,3 oraz grupy 2 B po stronie lewej wielkości 8x13 mm SUV max 4,6. Wzmożony metabolizm FDG w strukturach pierścienia Waldeyera SUV max do 8,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej, w lewej zatoce klinowej wydzielina śluzowa. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata - do kontroli w USG. Ok. 11mm brodawka skórna przynosowo po stronie lewej twarzy. Węzły chłonne na szyi obustronnie średnicy do 12mm.  Klatka piersiowa i śródpiersie: Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - opisywane już poprzednio. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 16mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Pęcherze rozedmowe w obu płucach, ocena utrudniona przez artefakty oddechowe. AGR Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatniejsze zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku SUV max 3,8. Guz nadnercza lewego, wielkości 26x18mm SUV max 2,5. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo. Wydatne pęcherzyki nasienne. Obustronnie węzły chłonne pachwinowe wielkości do 11mm.  Układ kostny: Wzmożony metabolizm FDG pomiędzy wyrostkami kolczystymi na poziomie L3/L4 SUV max 4,2- zmiany odczynowo-przeciążeniowe? Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Aktywnie metabolicznie obszar w topografii rozwastwionej, uwapnionej blaszki  miażdżycowej w tylnej ścianie aorty na poziomie Th12 wielkości 7x7mm wg. PET, SUV max 5,7 [Im fuz 154] Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,6.</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne grupy 2A po stronie prawej wielkości do 13 mm  SUV max do 7,3 oraz grupy 2 B po stronie lewej wielkości 8x13 mm SUV max 4,6. Wzmożony metabolizm FDG w strukturach pierścienia Waldeyera SUV max do 8,6. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Wydatne polipowate zgrubienia błony śluzowej w prawej zatoce szczękowej oraz drobne w lewej, w lewej zatoce klinowej wydzielina śluzowa. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata - do kontroli w USG. Ok. 11mm brodawka skórna przynosowo po stronie lewej twarzy. Węzły chłonne na szyi obustronnie średnicy do 12mm.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - opisywane już poprzednio. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywne metabolicznie węzły chłonne pachowe i przytchawicze dolne obustronnie wielkości do 16mm.  Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Pęcherze rozedmowe w obu płucach, ocena utrudniona przez artefakty oddechowe. AGR Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatniejsze zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Rozlanie wzmożony metabolizm FDG w żołądku SUV max 3,8. Guz nadnercza lewego, wielkości 26x18mm SUV max 2,5. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo. Wydatne pęcherzyki nasienne. Obustronnie węzły chłonne pachwinowe wielkości do 11mm.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG pomiędzy wyrostkami kolczystymi na poziomie L3/L4 SUV max 4,2- zmiany odczynowo-przeciążeniowe? Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Aktywnie metabolicznie obszar w topografii rozwastwionej, uwapnionej blaszki  miażdżycowej w tylnej ścianie aorty na poziomie Th12 wielkości 7x7mm wg. PET, SUV max 5,7 [Im fuz 154] Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnych metabolicznie drobnych węzłów chłonnych na szyi obustronnie - do weryfikacji histopatologicznej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="L9" t="n">
         <v>8.6</v>
       </c>
     </row>
@@ -733,20 +958,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 108 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>: Aktywne i pobudzone metabolicznie węzły chłonne szyjne: - węzły własne ślinianek przyusznych- po stronie prawej średnicy 15mm wg PET SUV max 4,1; po stronie lewej średnicy 9mm SUV max 2,9; - grupy 2A po stronie prawej wielkości10x8 mm  SUV max 9,8; - grupy 2A po stronie lewej wielkości 11x12 mm SUV max 6,0. Pobudzona metabolicznie brodawka skórna przynosowo po stronie lewej twarzy wielkości ok 10 mm SUV max 3,1. Wzmożony metabolizm FDG w strukturach pierścienia Waldeyera SUV max do 7,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Polipowate zgrubienie błony śluzowej w lewej zatoce klinowej.  Drobne, polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata - do kontroli w USG.  Klatka piersiowa i śródpiersie: Ogniskowo zwiększony metabolizm FDG zabrodawkowo w piersi lewej, na obszarze wielkości wg. PET 11mm, SUV max 3,5 - do kontroli w USG/Mammografii. Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - opisywane już poprzednio. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Nieliczne pęcherze rozedmowe w obu płucach. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatniejsze zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Odcinkowo wzmożony metabolizm FDG w jelitach położonych w miednicy, SUV max 6,9 Guz nadnercza lewego, wielkości 27x18mm, SUV max 2,7. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo. Wydatne pęcherzyki nasienne. Uchyłki esicy. Obustronnie węzły chłonne pachwinowe wielkości do 11x9mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2 do 15mm. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,8.</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Aktywne i pobudzone metabolicznie węzły chłonne szyjne: - węzły własne ślinianek przyusznych- po stronie prawej średnicy 15mm wg PET SUV max 4,1; po stronie lewej średnicy 9mm SUV max 2,9; - grupy 2A po stronie prawej wielkości10x8 mm  SUV max 9,8; - grupy 2A po stronie lewej wielkości 11x12 mm SUV max 6,0. Pobudzona metabolicznie brodawka skórna przynosowo po stronie lewej twarzy wielkości ok 10 mm SUV max 3,1. Wzmożony metabolizm FDG w strukturach pierścienia Waldeyera SUV max do 7,5. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony, miernie nasilony zanik podkorowo-korowy mózgu. Hypoplazja zatok czołowych. Polipowate zgrubienie błony śluzowej w lewej zatoce klinowej.  Drobne, polipowate zgrubienia błony śluzowej w obu zatokach szczękowych. Tarczyca miernie powiększona, zwłaszcza w zakresie prawego płata - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ogniskowo zwiększony metabolizm FDG zabrodawkowo w piersi lewej, na obszarze wielkości wg. PET 11mm, SUV max 3,5 - do kontroli w USG/Mammografii. Zwiększony metabolizm FDG w topografii wyraźnie pogrubiałego miokardium LK serca - kardiomiopatia przerostowa? przerost mięśnia lewej komory serca w przebiegu nadciśnienia tętniczego? - opisywane już poprzednio. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Niewielkie zmiany włókniste w szczytach obu płuc, z drobnymi zwapnieniami. Nieliczne pęcherze rozedmowe w obu płucach. Ok. 3mm zwapnienie w segm. 4 płuca lewego oraz 7mm w segm. 6 tego płuca. Wydatniejsze zmiany włókniste w segm. 5 płuca prawego, mniejsze po stronie lewej. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Odcinkowo wzmożony metabolizm FDG w jelitach położonych w miednicy, SUV max 6,9 Guz nadnercza lewego, wielkości 27x18mm, SUV max 2,7. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o nieco "pozaciąganych" pozapalnie obrysach z drobnymi zwapnieniami w miąższu, przymiedniczkowo. Wydatne pęcherzyki nasienne. Uchyłki esicy. Obustronnie węzły chłonne pachwinowe wielkości do 11x9mm.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa - największe w odcinku szyjnym, z dyskopatiami, wielopoziomowo. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Włamanie blaszki granicznej górnej, z obniżeniem wysokości trzonu kręgu L2 do 15mm. Wyspa kostna w prawobocznej części trzonu kręgu Th3. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnych metabolicznie węzłów chłonnych szyi i twarzoczaszki. Ogniskowo zwiększony metabolizm FDG zabrodawkowo w piersi lewej- do kontroli w USG/Mammografii. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="L10" t="n">
         <v>9.800000000000001</v>
       </c>
     </row>
